--- a/training_result/90/0/ac/parameters_4.xlsx
+++ b/training_result/90/0/ac/parameters_4.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C76"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,7 +443,7 @@
         <v>0.5</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -466,10 +466,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9856</v>
+        <v>0.9755</v>
       </c>
       <c r="C4" t="n">
-        <v>15.5445</v>
+        <v>9.9786</v>
       </c>
     </row>
     <row r="5">
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9508</v>
+        <v>0.9422</v>
       </c>
       <c r="C7" t="n">
-        <v>15.1389</v>
+        <v>8.015499999999999</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         <v>0.5</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0327</v>
+        <v>1.0265</v>
       </c>
     </row>
     <row r="9">
@@ -544,10 +544,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9845</v>
+        <v>0.984</v>
       </c>
       <c r="C10" t="n">
-        <v>28.0407</v>
+        <v>27.0789</v>
       </c>
     </row>
     <row r="11">
@@ -560,7 +560,7 @@
         <v>0.5</v>
       </c>
       <c r="C11" t="n">
-        <v>0.21</v>
+        <v>0.2142</v>
       </c>
     </row>
     <row r="12">
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9627</v>
+        <v>0.9619</v>
       </c>
       <c r="C13" t="n">
-        <v>5.4297</v>
+        <v>4.6856</v>
       </c>
     </row>
     <row r="14">
@@ -599,7 +599,7 @@
         <v>0.5</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.0452</v>
+        <v>-0.0449</v>
       </c>
     </row>
     <row r="15">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9493</v>
+        <v>0.9667</v>
       </c>
       <c r="C16" t="n">
-        <v>8.692</v>
+        <v>13.4666</v>
       </c>
     </row>
     <row r="17">
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.979</v>
+        <v>0.9588</v>
       </c>
       <c r="C19" t="n">
-        <v>16.387</v>
+        <v>8.711600000000001</v>
       </c>
     </row>
     <row r="20">
@@ -677,7 +677,7 @@
         <v>0.5</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1089</v>
+        <v>0.1141</v>
       </c>
     </row>
     <row r="21">
@@ -700,10 +700,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9631</v>
+        <v>0.98</v>
       </c>
       <c r="C22" t="n">
-        <v>8.2079</v>
+        <v>13.8365</v>
       </c>
     </row>
     <row r="23">
@@ -716,7 +716,7 @@
         <v>0.5</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.4994</v>
+        <v>-0.5004</v>
       </c>
     </row>
     <row r="24">
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9439</v>
+        <v>0.9462</v>
       </c>
       <c r="C25" t="n">
-        <v>17.9862</v>
+        <v>12.9697</v>
       </c>
     </row>
     <row r="26">
@@ -755,7 +755,7 @@
         <v>0.5</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1529</v>
+        <v>-0.1532</v>
       </c>
     </row>
     <row r="27">
@@ -778,10 +778,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.985</v>
+        <v>0.9826</v>
       </c>
       <c r="C28" t="n">
-        <v>16.873</v>
+        <v>14.6272</v>
       </c>
     </row>
     <row r="29">
@@ -794,7 +794,7 @@
         <v>0.5</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6166</v>
+        <v>0.6167</v>
       </c>
     </row>
     <row r="30">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9629</v>
+        <v>0.9637</v>
       </c>
       <c r="C31" t="n">
-        <v>14.2705</v>
+        <v>14.7267</v>
       </c>
     </row>
     <row r="32">
@@ -833,7 +833,7 @@
         <v>0.5</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0558</v>
+        <v>-0.056</v>
       </c>
     </row>
     <row r="33">
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.9736</v>
+        <v>0.9779</v>
       </c>
       <c r="C34" t="n">
-        <v>11.7213</v>
+        <v>14.0189</v>
       </c>
     </row>
     <row r="35">
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9823</v>
+        <v>0.9819</v>
       </c>
       <c r="C37" t="n">
-        <v>13.1728</v>
+        <v>12.9037</v>
       </c>
     </row>
     <row r="38">
@@ -911,7 +911,7 @@
         <v>0.5</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7059</v>
+        <v>0.7060999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9714</v>
+        <v>0.9751</v>
       </c>
       <c r="C40" t="n">
-        <v>9.9747</v>
+        <v>11.1908</v>
       </c>
     </row>
     <row r="41">
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9378</v>
+        <v>0.945</v>
       </c>
       <c r="C43" t="n">
-        <v>1.7567</v>
+        <v>3.418</v>
       </c>
     </row>
     <row r="44">
@@ -989,7 +989,7 @@
         <v>0.5</v>
       </c>
       <c r="C44" t="n">
-        <v>0.097</v>
+        <v>0.0979</v>
       </c>
     </row>
     <row r="45">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9468</v>
+        <v>0.9425</v>
       </c>
       <c r="C46" t="n">
-        <v>-2.0296</v>
+        <v>-2.3577</v>
       </c>
     </row>
     <row r="47">
@@ -1028,7 +1028,7 @@
         <v>0.5</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5085</v>
+        <v>0.5096000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.9569</v>
+        <v>0.9557</v>
       </c>
       <c r="C49" t="n">
-        <v>15.2336</v>
+        <v>14.8423</v>
       </c>
     </row>
     <row r="50">
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.9641</v>
+        <v>0.9742</v>
       </c>
       <c r="C52" t="n">
-        <v>10.3719</v>
+        <v>12.479</v>
       </c>
     </row>
     <row r="53">
@@ -1106,7 +1106,7 @@
         <v>0.5</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1267</v>
+        <v>-0.1282</v>
       </c>
     </row>
     <row r="54">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.9504</v>
+        <v>0.9606</v>
       </c>
       <c r="C55" t="n">
-        <v>-3.0055</v>
+        <v>-2.0435</v>
       </c>
     </row>
     <row r="56">
@@ -1145,7 +1145,7 @@
         <v>0.5</v>
       </c>
       <c r="C56" t="n">
-        <v>0.045</v>
+        <v>0.0451</v>
       </c>
     </row>
     <row r="57">
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.9268</v>
+        <v>0.9261</v>
       </c>
       <c r="C58" t="n">
-        <v>5.4349</v>
+        <v>5.3565</v>
       </c>
     </row>
     <row r="59">
@@ -1184,7 +1184,7 @@
         <v>0.5</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.0578</v>
+        <v>-0.057</v>
       </c>
     </row>
     <row r="60">
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.9577</v>
+        <v>0.9591</v>
       </c>
       <c r="C61" t="n">
-        <v>6.2593</v>
+        <v>6.4659</v>
       </c>
     </row>
     <row r="62">
@@ -1223,7 +1223,7 @@
         <v>0.5</v>
       </c>
       <c r="C62" t="n">
-        <v>0.2809</v>
+        <v>0.2823</v>
       </c>
     </row>
     <row r="63">
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.9096</v>
+        <v>0.8928</v>
       </c>
       <c r="C64" t="n">
-        <v>3.7127</v>
+        <v>3.2643</v>
       </c>
     </row>
     <row r="65">
@@ -1262,7 +1262,7 @@
         <v>0.5</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.0002</v>
+        <v>-0.0009</v>
       </c>
     </row>
     <row r="66">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.9073</v>
       </c>
       <c r="C67" t="n">
-        <v>5.6561</v>
+        <v>4.8118</v>
       </c>
     </row>
     <row r="68">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8589</v>
+        <v>0.8777</v>
       </c>
       <c r="C70" t="n">
-        <v>-1.8055</v>
+        <v>-1.8469</v>
       </c>
     </row>
     <row r="71">
@@ -1340,7 +1340,7 @@
         <v>0.5</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.009599999999999999</v>
       </c>
     </row>
     <row r="72">
@@ -1379,7 +1379,7 @@
         <v>0.5</v>
       </c>
       <c r="C74" t="n">
-        <v>0.2519</v>
+        <v>0.2505</v>
       </c>
     </row>
     <row r="75">
@@ -1398,14 +1398,92 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>第26站-other</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>第27站-1</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C76" t="n">
+      <c r="B77" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C77" t="n">
         <v>-0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>第27站-2</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>第27站-other</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>第28站-1</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>第28站-2</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>第28站-other</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
